--- a/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
+++ b/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.tan\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.tan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDCB00A-9219-40B2-A831-A1AC8C3827B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4150C297-12A3-4662-AE08-F798F165CF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{06FF8372-BE40-4131-8A7A-3985CA2894E8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="22">
   <si>
     <t>Signal</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>BCLK (Audio)</t>
+  </si>
+  <si>
+    <t>DetectCable (pull high to 3v3)</t>
   </si>
 </sst>
 </file>
@@ -505,11 +508,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>226695</xdr:colOff>
+      <xdr:colOff>216112</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2798445</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="256160" cy="264560"/>
+      <xdr:rowOff>2110528</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="313055" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="11" name="TextBox 10">
@@ -523,8 +526,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10256520" y="2979420"/>
-          <a:ext cx="256160" cy="264560"/>
+          <a:off x="10005695" y="2301028"/>
+          <a:ext cx="313055" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -548,11 +551,12 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-SG" sz="1100">
               <a:solidFill>
@@ -569,11 +573,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>56197</xdr:colOff>
+      <xdr:colOff>87947</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2813684</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="327654" cy="264560"/>
+      <xdr:rowOff>2083434</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="324803" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12" name="TextBox 11">
@@ -587,8 +591,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5637847" y="2994659"/>
-          <a:ext cx="327654" cy="264560"/>
+          <a:off x="5527780" y="2273934"/>
+          <a:ext cx="324803" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -612,11 +616,12 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-SG" sz="1100">
               <a:solidFill>
@@ -2766,256 +2771,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2407227</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>744682</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2415886</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>103909</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="49" name="Straight Connector 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2762245-DBBD-9E17-DF45-CCE533F834DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3532909" y="8771659"/>
-          <a:ext cx="8659" cy="2060864"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>744682</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>138545</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2355273</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>8659</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Straight Connector 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B26BA6C-5B96-A7FF-7857-71D481F1819B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="744682" y="10867159"/>
-          <a:ext cx="2736273" cy="2727614"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>744682</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>8659</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>744682</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Straight Connector 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634EB34B-9B3B-6095-078B-53FDEA9CC686}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="744682" y="13594773"/>
-          <a:ext cx="0" cy="4468091"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>727364</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>917864</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>121227</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="57" name="Straight Connector 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19EAA985-2646-EC65-762E-0B8F06F052ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="727364" y="18062864"/>
-          <a:ext cx="190500" cy="216477"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>943841</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>147204</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>337704</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>147204</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="Straight Connector 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B2B5461-6973-FD6F-06A8-C05DE3A0032E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="943841" y="18305318"/>
-          <a:ext cx="519545" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3252,7 +3007,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-SG" sz="800" b="0" u="none">
+            <a:rPr lang="en-SG" sz="800" b="1" u="sng">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -3328,74 +3083,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>749011</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>334240</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="271896" cy="468013"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="TextBox 65">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA5DFED-1F9C-4294-A249-415255A05CA7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1874693" y="8361217"/>
-          <a:ext cx="271896" cy="468013"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-SG" sz="2400">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>X</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2541442</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1390648</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="870240" cy="468013"/>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>932775</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1591731</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="870240" cy="718466"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="67" name="TextBox 66">
@@ -3409,8 +3102,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3667124" y="9417625"/>
-          <a:ext cx="870240" cy="468013"/>
+          <a:off x="7642608" y="1782231"/>
+          <a:ext cx="870240" cy="718466"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3463,7 +3156,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-SG" sz="800" b="0" u="none">
+            <a:rPr lang="en-SG" sz="800" b="1" u="none">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3474,7 +3167,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-SG" sz="800" b="0" u="none">
+            <a:rPr lang="en-SG" sz="800" b="1" u="none">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3482,784 +3175,21 @@
             <a:t>GND</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-SG" sz="800" b="0" u="none">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>* connect to motherboard</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>928687</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2833687</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2314575</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="69" name="Straight Connector 68">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3919718-4061-CADA-B9EB-9DE1531F0190}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="30" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="7620000" y="3024187"/>
-          <a:ext cx="1385888" cy="5448301"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1452562</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2857500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1814513</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>519114</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="70" name="Straight Connector 69">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71E718EA-83B7-4B1F-9FD9-65EFAF45AF4A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="8143875" y="3048000"/>
-          <a:ext cx="361951" cy="5495927"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2868083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1788584</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>531021</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="72" name="Straight Connector 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{028959FE-17D2-46A7-B733-F1500AE66AD8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8071908" y="3058583"/>
-          <a:ext cx="426509" cy="5505188"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>814917</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2836333</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1241426</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>499271</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="74" name="Straight Connector 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5E61C8-09DA-4F45-B873-0D3F9C8D7DC4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7524750" y="3026833"/>
-          <a:ext cx="426509" cy="5505188"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>338667</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2825750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2053167</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>541604</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="75" name="Straight Connector 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E250D77B-5ABB-4777-95E7-0932459F3DA9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7048500" y="3016250"/>
-          <a:ext cx="1714500" cy="5558104"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1090084</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2899833</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>520437</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="77" name="Straight Connector 76">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9ED8DF5-3ECB-423B-B069-55609D8DA517}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="6529917" y="3090333"/>
-          <a:ext cx="2804583" cy="5462854"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>582084</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2857500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2338917</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>509854</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="79" name="Straight Connector 78">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91AD85BD-D109-47B3-B78C-543F0127CEC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="6021917" y="3048000"/>
-          <a:ext cx="3026833" cy="5494604"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>74084</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2868083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>456937</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="81" name="Straight Connector 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F27D9B35-F0F8-401A-8D6E-488BE086D05E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5513917" y="3058583"/>
-          <a:ext cx="4138083" cy="5431104"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>179917</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2857500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>370417</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>488687</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="83" name="Straight Connector 82">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B62E5CBD-15A7-4FCC-8124-1FBB07D89B11}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5005917" y="3048000"/>
-          <a:ext cx="2074333" cy="5473437"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2952750</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2868083</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>467521</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="85" name="Straight Connector 84">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD767367-AE43-4A21-B444-07E810A2CE1D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4074583" y="3058583"/>
-          <a:ext cx="5873750" cy="5441688"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2391834</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2836333</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>105834</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>478105</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="87" name="Straight Connector 86">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{296F7FC5-6AA5-4EE0-BD31-150549714A9D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3513667" y="3026833"/>
-          <a:ext cx="3302000" cy="5484022"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1915583</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2910417</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1079500</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>488689</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="89" name="Straight Connector 88">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7DF17E9-6152-42B5-9869-1C02133C69A4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3037416" y="3100917"/>
-          <a:ext cx="3481917" cy="5420522"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1407583</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2921000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>772584</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>488689</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="91" name="Straight Connector 90">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7547C7-C3EF-401E-8C81-436078426441}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2529416" y="3111500"/>
-          <a:ext cx="3683001" cy="5409939"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>433916</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3078244</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>220024</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>541605</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="93" name="Straight Connector 92">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32EA12C0-F2F7-42AC-AEC5-3A9361F93CAC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:endCxn id="12" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1555749" y="3268744"/>
-          <a:ext cx="4104108" cy="5305611"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4319,6 +3249,997 @@
             </a:rPr>
             <a:t>GND</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>946869</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>655709</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2942314</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>667833</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="Connector: Elbow 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDD40539-7477-FA8D-BCA6-46B1C892A08D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="63" idx="2"/>
+          <a:endCxn id="42" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="3060363" y="7696798"/>
+          <a:ext cx="12124" cy="1995445"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -1885516"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>434686</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2921000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>243417</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>446810</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="Straight Arrow Connector 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC1E83D7-A359-2CBB-9741-14F4F46A4EF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="64" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1556519" y="3111500"/>
+          <a:ext cx="4126731" cy="5368060"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1452561</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2973917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>793750</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>427759</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="71" name="Straight Arrow Connector 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C1E3945-7E4C-4351-834C-254449BF6B8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="62" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2574394" y="3164417"/>
+          <a:ext cx="3659189" cy="5296092"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1949593</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2963333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1079500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>431222</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="82" name="Straight Arrow Connector 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27400B58-560B-4B4B-A820-7DB61EF93122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="61" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3071426" y="3153833"/>
+          <a:ext cx="3447907" cy="5310139"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2437966</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2963333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>434686</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="88" name="Straight Arrow Connector 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C8B5D6-F6AD-42BC-8CC0-1AB5D595D98B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="60" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3559799" y="3153833"/>
+          <a:ext cx="3277034" cy="5313603"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2942315</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2963333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>105834</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>438149</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="97" name="Straight Arrow Connector 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51855268-1946-48F1-A7C2-AC7B282EF1FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="42" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4064148" y="3153833"/>
+          <a:ext cx="5831269" cy="5317066"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>243017</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2942167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>359834</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>449406</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="103" name="Straight Arrow Connector 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5DBA42E-0B55-4606-ADFB-2CD2A83E83E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="39" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5069017" y="3132667"/>
+          <a:ext cx="2000650" cy="5349489"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>116417</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2952750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>423333</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="106" name="Straight Arrow Connector 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1209A044-8F06-4DAC-B5FC-92CB5FBBBF1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5556250" y="3143250"/>
+          <a:ext cx="4064000" cy="5312833"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>592716</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2952750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2349500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>436419</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="111" name="Straight Arrow Connector 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2AB621C-3DDA-4671-BB2B-242F265129D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="37" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6032549" y="3143250"/>
+          <a:ext cx="3026784" cy="5325919"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1096676</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2952750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>431223</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="114" name="Straight Arrow Connector 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA3CDAF-07C2-4816-BB8A-9C995F052F17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6536509" y="3143250"/>
+          <a:ext cx="2797991" cy="5320723"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>328180</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2973917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2053167</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>452005</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="119" name="Straight Arrow Connector 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{353F6915-D2DA-454B-A6E4-BB259B7F9CD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="35" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7038013" y="3164417"/>
+          <a:ext cx="1724987" cy="5320338"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>825212</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2942167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1227667</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>446809</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="122" name="Straight Arrow Connector 121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62DBD95F-FB21-46E5-B418-F19C9F1D3923}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="34" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7535045" y="3132667"/>
+          <a:ext cx="402455" cy="5346892"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1313585</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2952750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1788584</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>450273</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="125" name="Straight Arrow Connector 124">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{543394B2-308F-4D53-B657-CE345E0486BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="33" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8023418" y="3143250"/>
+          <a:ext cx="474999" cy="5339773"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1460500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2952750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1842221</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>449406</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="129" name="Straight Arrow Connector 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CBC65E2-854D-4631-8D31-CB521B8B8D12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8170333" y="3143250"/>
+          <a:ext cx="381721" cy="5338906"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>920750</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2942167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2314575</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="132" name="Straight Arrow Connector 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B4CD864-C208-47CC-A8FE-D79EAE0771BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="30" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7630583" y="3132667"/>
+          <a:ext cx="1393825" cy="5347758"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1476374</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>929793</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="904875" cy="593239"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="137" name="TextBox 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39D251D3-062B-48AD-975D-7C56EF425E00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2598207" y="8962543"/>
+          <a:ext cx="904875" cy="593239"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-SG" sz="800" b="0" u="none">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Pull</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-SG" sz="800" b="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Cable-Detect High to 3v3 to enable 480p options</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-SG" sz="800" b="0" u="none">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4682,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C4" t="e">
         <f>_xlfn.XLOOKUP(B4,E:E,D:D)</f>
@@ -5093,6 +5014,9 @@
       <c r="I18" s="1">
         <v>15</v>
       </c>
+      <c r="J18" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -5117,6 +5041,9 @@
       </c>
       <c r="I19" s="1">
         <v>16</v>
+      </c>
+      <c r="J19" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">

--- a/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
+++ b/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.tan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4150C297-12A3-4662-AE08-F798F165CF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DB9610-A47E-4F69-BCFB-96DA5B1A666E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{06FF8372-BE40-4131-8A7A-3985CA2894E8}"/>
   </bookViews>
@@ -196,6 +196,57 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3354383</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3026301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>74082</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>620550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{589BD00B-43E6-1E90-BC04-7B1018210745}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:alphaModFix amt="10000"/>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="4476216" y="3216801"/>
+          <a:ext cx="6615116" cy="5436499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>446622</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -221,7 +272,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -271,7 +322,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -332,7 +383,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -382,7 +433,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -432,7 +483,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -482,7 +533,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4238,6 +4289,168 @@
           <a:endParaRPr lang="en-SG" sz="800" b="0" u="none">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>587372</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>9043</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2883960" cy="874920"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="TextBox 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC68381-229E-42CB-93B0-399804AAD622}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6027205" y="19704626"/>
+          <a:ext cx="2883960" cy="874920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-SG" sz="1000" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CDET can</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-SG" sz="1000" b="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> be connected directly to 3v3 to pull it high to enable 480p options, so routing it to a soldering pad above is unnecessary. Instead, you can repurpose the CDET pad above as a GND pad for alignment to the main board</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-SG" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>920750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2883960" cy="405367"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{646B23FF-BC8C-48E9-8C25-4E5EC1AA4D65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11176000" y="1111250"/>
+          <a:ext cx="2883960" cy="405367"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-SG" sz="1000" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>The breakout</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-SG" sz="1000" b="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> board is used for easier visualization  for the mappings</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-SG" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>

--- a/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
+++ b/PCB/DOL-101/DOL-101 Digital AV Flex Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.tan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.tan\Documents\GCHDMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DB9610-A47E-4F69-BCFB-96DA5B1A666E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED01C13-BFA5-4D21-9753-A00F415CC982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{06FF8372-BE40-4131-8A7A-3985CA2894E8}"/>
   </bookViews>
@@ -222,7 +222,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:alphaModFix amt="10000"/>
+          <a:alphaModFix amt="20000"/>
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -396,8 +396,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="5603557" y="171449"/>
-          <a:ext cx="5624370" cy="3117532"/>
+          <a:off x="5461740" y="171449"/>
+          <a:ext cx="5530179" cy="3127057"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3135,9 +3135,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>932775</xdr:colOff>
+      <xdr:colOff>2382692</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1591731</xdr:rowOff>
+      <xdr:rowOff>1644648</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="870240" cy="718466"/>
     <xdr:sp macro="" textlink="">
@@ -3153,7 +3153,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7642608" y="1782231"/>
+          <a:off x="9092525" y="1835148"/>
           <a:ext cx="870240" cy="718466"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
